--- a/feedback_surveys/006_saddle_bench_feedback_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/006_saddle_bench_feedback_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>question1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How satisfied are you</t>
+          <t>How satisfied are you with the saddle bench experience?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>comfort</t>
+          <t>question2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How comfortable are you with the saddle</t>
+          <t>How comfortable did you feel using the saddle?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>improvement</t>
+          <t>question3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How can we improve the saddle?</t>
+          <t>What did you find most helpful in improving the saddle?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>question4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How can we contact you?</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>question5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>question6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rating (1-5)</t>
+          <t>Rate your experience (1-5)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>question7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Which facility?</t>
+          <t>Which facility used the saddle?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>question8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Which department?</t>
+          <t>Which department used the saddle?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>shift</t>
+          <t>question9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Which shift?</t>
+          <t>Which shift did you work on?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_shift</t>
+          <t>question10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How often do you work on this shift?</t>
+          <t>How often do you use the saddle?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_time</t>
+          <t>question11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_date</t>
+          <t>question12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>question13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_other</t>
+          <t>question14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>additional_comments_2</t>
+          <t>question15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Question15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>question16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rating (1-5)</t>
+          <t>Question16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>facility_2</t>
+          <t>question17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Which facility?</t>
+          <t>Question17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>department_2</t>
+          <t>question18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Which department?</t>
+          <t>Question18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>shift_2</t>
+          <t>question19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Which shift?</t>
+          <t>Which shift used the saddle?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contact_shift_2</t>
+          <t>question20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How often do you work on this shift?</t>
+          <t>Question20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contact_time_2</t>
+          <t>question21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What time do you contact us?</t>
+          <t>Question21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>contact_date_2</t>
+          <t>question22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>On which date do you contact us?</t>
+          <t>Question22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_method_2</t>
+          <t>question23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How do you contact us?</t>
+          <t>Question23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>contact_other_2</t>
+          <t>question24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Do you have any other contact preferences?</t>
+          <t>Question24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>question1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>comfort_choices</t>
+          <t>question2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>facility_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>facility_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>facility_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>facility_choices</t>
+          <t>question7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>question8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>shift_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>shift_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>shift_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>shift_choices</t>
+          <t>question9_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>contact_shift_choices</t>
+          <t>question10_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>contact_shift_choices</t>
+          <t>question10_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>contact_shift_choices</t>
+          <t>question10_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>contact_shift_choices</t>
+          <t>question10_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>question13_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>question13_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>question13_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>contact_other_choices</t>
+          <t>question14_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>contact_other_choices</t>
+          <t>question14_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>facility_2_choices</t>
+          <t>question17_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>facility_2_choices</t>
+          <t>question17_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>facility_2_choices</t>
+          <t>question17_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>facility_2_choices</t>
+          <t>question17_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>department_2_choices</t>
+          <t>question18_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>department_2_choices</t>
+          <t>question18_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>department_2_choices</t>
+          <t>question18_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>department_2_choices</t>
+          <t>question18_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>shift_2_choices</t>
+          <t>question19_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>shift_2_choices</t>
+          <t>question19_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>shift_2_choices</t>
+          <t>question19_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>shift_2_choices</t>
+          <t>question19_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>contact_shift_2_choices</t>
+          <t>question20_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>contact_shift_2_choices</t>
+          <t>question20_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>contact_shift_2_choices</t>
+          <t>question20_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1908,7 +1908,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>contact_shift_2_choices</t>
+          <t>question20_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1925,7 +1925,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>contact_method_2_choices</t>
+          <t>question23_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>contact_method_2_choices</t>
+          <t>question23_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>contact_method_2_choices</t>
+          <t>question23_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>contact_other_2_choices</t>
+          <t>question24_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>contact_other_2_choices</t>
+          <t>question24_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
